--- a/data/trans_orig/P04D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37809</t>
+          <t>38198</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67417</t>
+          <t>66042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60048</t>
+          <t>59278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94800</t>
+          <t>94231</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>105809</t>
+          <t>104459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150851</t>
+          <t>149083</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>684747</t>
+          <t>685624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>741443</t>
+          <t>742672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>928980</t>
+          <t>930500</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>995861</t>
+          <t>996127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1630992</t>
+          <t>1630825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1723300</t>
+          <t>1721065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,53%</t>
+          <t>70,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,52%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>185124</t>
+          <t>181455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>236434</t>
+          <t>236610</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>268131</t>
+          <t>267823</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>327136</t>
+          <t>327916</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>467293</t>
+          <t>468776</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>551129</t>
+          <t>548381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61685</t>
+          <t>61387</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100323</t>
+          <t>98688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56972</t>
+          <t>58023</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>91290</t>
+          <t>92706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>126065</t>
+          <t>130251</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179116</t>
+          <t>177915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1157396</t>
+          <t>1154366</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1249112</t>
+          <t>1244605</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1043461</t>
+          <t>1047293</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1134092</t>
+          <t>1126451</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2230887</t>
+          <t>2230313</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2349321</t>
+          <t>2353441</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,23%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>638492</t>
+          <t>637986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>723451</t>
+          <t>726400</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,51%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>555793</t>
+          <t>555761</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>637774</t>
+          <t>638556</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1225924</t>
+          <t>1220866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1340092</t>
+          <t>1337691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>23147</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5144</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19401</t>
+          <t>19864</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13547</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209186</t>
+          <t>211979</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>256384</t>
+          <t>259054</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>215998</t>
+          <t>216388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>261832</t>
+          <t>262131</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>438353</t>
+          <t>441711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>503836</t>
+          <t>505694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>213059</t>
+          <t>212153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259866</t>
+          <t>256425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187053</t>
+          <t>184779</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>233330</t>
+          <t>231638</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>411822</t>
+          <t>410511</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>478003</t>
+          <t>475252</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,57%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>117502</t>
+          <t>119311</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>166579</t>
+          <t>168965</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135365</t>
+          <t>137454</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>185471</t>
+          <t>187183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268796</t>
+          <t>268049</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>336416</t>
+          <t>340093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2096576</t>
+          <t>2095041</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2213996</t>
+          <t>2212054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2228356</t>
+          <t>2232481</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2345728</t>
+          <t>2350283</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4359423</t>
+          <t>4352626</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4522719</t>
+          <t>4528360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>64,93%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1073044</t>
+          <t>1068266</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1186073</t>
+          <t>1182727</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1048098</t>
+          <t>1046632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1159927</t>
+          <t>1161332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2150055</t>
+          <t>2146603</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2313094</t>
+          <t>2307629</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,09%</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>141918</t>
+          <t>142334</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188644</t>
+          <t>189113</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>182182</t>
+          <t>180077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>234599</t>
+          <t>233633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>339471</t>
+          <t>336252</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>408032</t>
+          <t>404797</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,14%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>433127</t>
+          <t>430022</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>487571</t>
+          <t>484106</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533262</t>
+          <t>536610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>600469</t>
+          <t>601372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>987758</t>
+          <t>984102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1073082</t>
+          <t>1066137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>60,96%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>111311</t>
+          <t>112090</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>152248</t>
+          <t>150899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>193738</t>
+          <t>194441</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>248581</t>
+          <t>247379</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>314429</t>
+          <t>320332</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>388357</t>
+          <t>388246</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282042</t>
+          <t>287533</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354716</t>
+          <t>354680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>218564</t>
+          <t>217305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278956</t>
+          <t>278738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>520659</t>
+          <t>519531</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>610597</t>
+          <t>609436</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1023117</t>
+          <t>1023792</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1113414</t>
+          <t>1119473</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>985102</t>
+          <t>985036</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1077024</t>
+          <t>1073999</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2036489</t>
+          <t>2038625</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2156342</t>
+          <t>2168356</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>641055</t>
+          <t>641453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>727579</t>
+          <t>728134</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>667893</t>
+          <t>670912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>759795</t>
+          <t>759213</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1337369</t>
+          <t>1335522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1458509</t>
+          <t>1458123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35566</t>
+          <t>35959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65622</t>
+          <t>65373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44319</t>
+          <t>43593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>71963</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>86882</t>
+          <t>88562</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>125932</t>
+          <t>129585</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>228553</t>
+          <t>230561</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>278646</t>
+          <t>279126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>223175</t>
+          <t>222899</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>270100</t>
+          <t>268834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>469445</t>
+          <t>467428</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>533680</t>
+          <t>536171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>217253</t>
+          <t>218704</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>268684</t>
+          <t>267733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223298</t>
+          <t>223462</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>272094</t>
+          <t>268649</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>458474</t>
+          <t>453433</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>522158</t>
+          <t>521954</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,62%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>487341</t>
+          <t>491340</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>577691</t>
+          <t>575975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>468625</t>
+          <t>471900</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>557047</t>
+          <t>553808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>986121</t>
+          <t>988780</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1110421</t>
+          <t>1118834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1718932</t>
+          <t>1730302</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1840884</t>
+          <t>1844535</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1779803</t>
+          <t>1781342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1901185</t>
+          <t>1899723</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3532897</t>
+          <t>3544069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3706486</t>
+          <t>3703882</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,6%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1004976</t>
+          <t>1008748</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1116986</t>
+          <t>1118852</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1125489</t>
+          <t>1121723</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1242343</t>
+          <t>1238112</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2165002</t>
+          <t>2156556</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2326765</t>
+          <t>2310980</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,45%</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023</t>
+          <t>Población según si disponen de algún tipo de calefacción (individual, colectiva o con aparatos) en la vivenda en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>52524</t>
+          <t>54353</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86036</t>
+          <t>88185</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78899</t>
+          <t>77956</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105696</t>
+          <t>104135</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139752</t>
+          <t>135825</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181245</t>
+          <t>180091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4927,12 +4927,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -4955,12 +4955,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>342637</t>
+          <t>339891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>380470</t>
+          <t>381183</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>550184</t>
+          <t>551081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>586412</t>
+          <t>587299</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5025,12 +5025,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>903740</t>
+          <t>903312</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>957774</t>
+          <t>957688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,44%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68975</t>
+          <t>68351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99557</t>
+          <t>99935</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81837</t>
+          <t>81167</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110432</t>
+          <t>110431</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>159570</t>
+          <t>158934</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>201014</t>
+          <t>200444</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -5298,12 +5298,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>168671</t>
+          <t>155549</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279932</t>
+          <t>281723</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>195955</t>
+          <t>200922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498810</t>
+          <t>495822</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>418796</t>
+          <t>415815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>715207</t>
+          <t>729086</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -5411,12 +5411,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>921172</t>
+          <t>916527</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1526346</t>
+          <t>1531246</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1390425</t>
+          <t>1392680</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1713039</t>
+          <t>1692779</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2421753</t>
+          <t>2263508</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3115457</t>
+          <t>3097427</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,4%</t>
         </is>
       </c>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>500144</t>
+          <t>504079</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1193039</t>
+          <t>1221873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>313172</t>
+          <t>325035</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>488517</t>
+          <t>491461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>911272</t>
+          <t>916845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1722403</t>
+          <t>1819906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42905</t>
+          <t>42592</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>75876</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55605</t>
+          <t>55926</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85706</t>
+          <t>84588</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>106121</t>
+          <t>107132</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>151956</t>
+          <t>149349</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -5867,12 +5867,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>312395</t>
+          <t>319234</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>368398</t>
+          <t>373034</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>300635</t>
+          <t>302783</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>347687</t>
+          <t>347517</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>633783</t>
+          <t>637113</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>705148</t>
+          <t>704476</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -5980,12 +5980,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>220720</t>
+          <t>219503</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>272272</t>
+          <t>269698</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243746</t>
+          <t>243129</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>291546</t>
+          <t>288965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>476920</t>
+          <t>477732</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>546234</t>
+          <t>541936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6065,12 +6065,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -6210,12 +6210,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>277762</t>
+          <t>274995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>409839</t>
+          <t>410112</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -6245,12 +6245,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>355014</t>
+          <t>361975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>668372</t>
+          <t>650227</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6280,12 +6280,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>698871</t>
+          <t>696514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1036240</t>
+          <t>1007010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -6323,12 +6323,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1542112</t>
+          <t>1555254</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2229428</t>
+          <t>2231257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6338,12 +6338,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6358,12 +6358,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2284568</t>
+          <t>2291512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2640427</t>
+          <t>2641834</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6373,12 +6373,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6393,12 +6393,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3923958</t>
+          <t>3946073</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4723578</t>
+          <t>4718416</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -6436,12 +6436,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>836623</t>
+          <t>833796</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1646094</t>
+          <t>1623220</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6451,12 +6451,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>640768</t>
+          <t>651072</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>858659</t>
+          <t>857734</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6486,12 +6486,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1595381</t>
+          <t>1602955</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2532746</t>
+          <t>2546583</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P04D_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38198</t>
+          <t>39109</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66042</t>
+          <t>64893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59278</t>
+          <t>60223</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94231</t>
+          <t>93693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104459</t>
+          <t>106549</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>149083</t>
+          <t>150155</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>685624</t>
+          <t>684781</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>742672</t>
+          <t>743190</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>930500</t>
+          <t>928175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>996127</t>
+          <t>993869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1630825</t>
+          <t>1629397</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1721065</t>
+          <t>1723372</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>181455</t>
+          <t>183934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>236610</t>
+          <t>239088</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>267823</t>
+          <t>268749</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>327916</t>
+          <t>328492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>468776</t>
+          <t>467025</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>548381</t>
+          <t>548629</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,73%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>61387</t>
+          <t>63327</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>98688</t>
+          <t>103014</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>58023</t>
+          <t>57369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92706</t>
+          <t>92978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>130251</t>
+          <t>128888</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177915</t>
+          <t>181378</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,87%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1154366</t>
+          <t>1156916</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1244605</t>
+          <t>1247055</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1047293</t>
+          <t>1048379</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1126451</t>
+          <t>1132429</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,64%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2230313</t>
+          <t>2226456</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2353441</t>
+          <t>2346599</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,05%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>637986</t>
+          <t>640912</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>726400</t>
+          <t>725769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>555761</t>
+          <t>553829</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>638556</t>
+          <t>634854</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1220866</t>
+          <t>1221381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1337691</t>
+          <t>1339784</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6515</t>
+          <t>5996</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23147</t>
+          <t>21163</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>19758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13934</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>35192</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211979</t>
+          <t>211909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>259054</t>
+          <t>256876</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>216388</t>
+          <t>215283</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>262131</t>
+          <t>260008</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>441711</t>
+          <t>439681</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>505694</t>
+          <t>503804</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>53,61%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212153</t>
+          <t>211149</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>256425</t>
+          <t>258713</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>184779</t>
+          <t>186198</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>231638</t>
+          <t>231137</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>410511</t>
+          <t>415217</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>475252</t>
+          <t>478489</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,91%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>119311</t>
+          <t>119761</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>168965</t>
+          <t>169405</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>137454</t>
+          <t>134983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>187183</t>
+          <t>185852</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>268049</t>
+          <t>268530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>340093</t>
+          <t>342934</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2095041</t>
+          <t>2091610</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2212054</t>
+          <t>2209442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2232481</t>
+          <t>2237538</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2350283</t>
+          <t>2350081</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4352626</t>
+          <t>4355158</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4528360</t>
+          <t>4525042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,88%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1068266</t>
+          <t>1067370</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1182727</t>
+          <t>1184849</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1046632</t>
+          <t>1048465</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1161332</t>
+          <t>1158312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2146603</t>
+          <t>2156618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2307629</t>
+          <t>2319007</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>142334</t>
+          <t>143771</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>189113</t>
+          <t>188121</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>180077</t>
+          <t>182056</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>233633</t>
+          <t>232295</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>336252</t>
+          <t>335139</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>404797</t>
+          <t>407277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>430022</t>
+          <t>432361</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484106</t>
+          <t>486976</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>536610</t>
+          <t>531911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>601372</t>
+          <t>594613</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>984102</t>
+          <t>982368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1066137</t>
+          <t>1067498</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112090</t>
+          <t>110779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>150899</t>
+          <t>153384</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>194441</t>
+          <t>196014</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>247379</t>
+          <t>253586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>320332</t>
+          <t>320275</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>388246</t>
+          <t>388734</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>287533</t>
+          <t>287056</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>354680</t>
+          <t>355565</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>217305</t>
+          <t>221840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278738</t>
+          <t>281012</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>519531</t>
+          <t>522272</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>609436</t>
+          <t>611748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1023792</t>
+          <t>1023602</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1119473</t>
+          <t>1116061</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>985036</t>
+          <t>981708</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1073999</t>
+          <t>1072821</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2038625</t>
+          <t>2036178</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2168356</t>
+          <t>2163796</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>641453</t>
+          <t>643251</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>728134</t>
+          <t>732124</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>670912</t>
+          <t>670722</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>759213</t>
+          <t>759539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1335522</t>
+          <t>1339432</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1458123</t>
+          <t>1462280</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -3699,12 +3699,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>36533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65373</t>
+          <t>66454</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>43593</t>
+          <t>44243</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71963</t>
+          <t>73597</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>88562</t>
+          <t>87514</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>129585</t>
+          <t>126872</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230561</t>
+          <t>231075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>279126</t>
+          <t>281621</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3827,12 +3827,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>222899</t>
+          <t>222333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>268834</t>
+          <t>269123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>467428</t>
+          <t>465099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>536171</t>
+          <t>534900</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3897,12 +3897,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>218704</t>
+          <t>215905</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>267733</t>
+          <t>266450</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,96%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223462</t>
+          <t>222186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268649</t>
+          <t>269827</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>453433</t>
+          <t>455064</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>521954</t>
+          <t>525433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>47,94%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>491340</t>
+          <t>491109</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>575975</t>
+          <t>578094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>471900</t>
+          <t>469694</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>553808</t>
+          <t>553359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>988780</t>
+          <t>984658</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1118834</t>
+          <t>1104253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -4268,12 +4268,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1730302</t>
+          <t>1723880</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1844535</t>
+          <t>1844014</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1781342</t>
+          <t>1780857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1899723</t>
+          <t>1896664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3544069</t>
+          <t>3533749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3703882</t>
+          <t>3710563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4353,12 +4353,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,6%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1008748</t>
+          <t>1005908</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1118852</t>
+          <t>1118700</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1121723</t>
+          <t>1121481</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1238112</t>
+          <t>1238252</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2156556</t>
+          <t>2163344</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2310980</t>
+          <t>2326654</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,67%</t>
         </is>
       </c>
     </row>
@@ -4837,32 +4837,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68152</t>
+          <t>82314</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54353</t>
+          <t>65426</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88185</t>
+          <t>101996</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4872,32 +4872,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>91061</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77956</t>
+          <t>91250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104135</t>
+          <t>121934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4907,32 +4907,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>159213</t>
+          <t>187704</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135825</t>
+          <t>166511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180091</t>
+          <t>211936</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -4950,32 +4950,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>362680</t>
+          <t>405703</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>339891</t>
+          <t>383985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381183</t>
+          <t>428963</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4985,32 +4985,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>568757</t>
+          <t>615521</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>551081</t>
+          <t>595298</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>587299</t>
+          <t>634101</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5020,32 +5020,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>931437</t>
+          <t>1021224</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>903312</t>
+          <t>990905</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>957688</t>
+          <t>1052228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>73,37%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -5063,32 +5063,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83088</t>
+          <t>89427</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>68351</t>
+          <t>72912</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99935</t>
+          <t>106651</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5098,32 +5098,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>95690</t>
+          <t>101128</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81167</t>
+          <t>87991</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>110431</t>
+          <t>116411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5133,32 +5133,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>178777</t>
+          <t>190555</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>158934</t>
+          <t>167759</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>200444</t>
+          <t>213794</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -5176,17 +5176,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513919</t>
+          <t>577444</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5246,17 +5246,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1269427</t>
+          <t>1399482</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1269427</t>
+          <t>1399482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1269427</t>
+          <t>1399482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5293,32 +5293,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>233623</t>
+          <t>272865</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>155549</t>
+          <t>239490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>281723</t>
+          <t>313842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5328,32 +5328,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>282914</t>
+          <t>268239</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>200922</t>
+          <t>241789</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>495822</t>
+          <t>299256</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5363,32 +5363,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>516537</t>
+          <t>541103</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>415815</t>
+          <t>495858</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>729086</t>
+          <t>589057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -5406,32 +5406,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1348107</t>
+          <t>1464980</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>916527</t>
+          <t>1409608</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1531246</t>
+          <t>1518638</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5441,32 +5441,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1527553</t>
+          <t>1444878</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1392680</t>
+          <t>1404964</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1692779</t>
+          <t>1485278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>68,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5476,32 +5476,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2875660</t>
+          <t>2909859</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2263508</t>
+          <t>2839770</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3097427</t>
+          <t>2976606</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>67,62%</t>
         </is>
       </c>
     </row>
@@ -5519,32 +5519,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>708597</t>
+          <t>492721</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>504079</t>
+          <t>446035</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1221873</t>
+          <t>541174</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5554,32 +5554,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>427357</t>
+          <t>458275</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>325035</t>
+          <t>424575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>491461</t>
+          <t>496414</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5589,32 +5589,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1135953</t>
+          <t>950997</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>916845</t>
+          <t>897185</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1819906</t>
+          <t>1014106</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -5632,17 +5632,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5667,17 +5667,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5702,17 +5702,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5749,32 +5749,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57579</t>
+          <t>76114</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42592</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75876</t>
+          <t>99032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>69265</t>
+          <t>81834</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55926</t>
+          <t>66906</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84588</t>
+          <t>98415</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5819,32 +5819,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>126844</t>
+          <t>157948</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>107132</t>
+          <t>134638</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>149349</t>
+          <t>182316</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>12,6%</t>
         </is>
       </c>
     </row>
@@ -5862,32 +5862,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>343848</t>
+          <t>376206</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319234</t>
+          <t>348773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>373034</t>
+          <t>406619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5897,32 +5897,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>325267</t>
+          <t>357101</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>302783</t>
+          <t>333735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>347517</t>
+          <t>380605</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5932,32 +5932,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>669115</t>
+          <t>733307</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>637113</t>
+          <t>693194</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>704476</t>
+          <t>769647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,21%</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5975,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>245196</t>
+          <t>259267</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>219503</t>
+          <t>234996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>269698</t>
+          <t>287336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>36,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6010,32 +6010,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>265931</t>
+          <t>295942</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243129</t>
+          <t>275740</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>288965</t>
+          <t>320548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6045,32 +6045,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>511127</t>
+          <t>555208</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>477732</t>
+          <t>514329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>541936</t>
+          <t>594023</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,07%</t>
         </is>
       </c>
     </row>
@@ -6088,17 +6088,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6123,17 +6123,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6158,17 +6158,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6205,32 +6205,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>359354</t>
+          <t>431293</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>274995</t>
+          <t>389148</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>410112</t>
+          <t>478287</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6240,32 +6240,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>443240</t>
+          <t>455462</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>361975</t>
+          <t>417850</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>650227</t>
+          <t>492382</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6275,32 +6275,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>802593</t>
+          <t>886755</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>696514</t>
+          <t>831261</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1007010</t>
+          <t>950798</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -6318,32 +6318,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2054635</t>
+          <t>2246889</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1555254</t>
+          <t>2179209</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2231257</t>
+          <t>2304787</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6353,32 +6353,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2421577</t>
+          <t>2417500</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2291512</t>
+          <t>2368932</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2641834</t>
+          <t>2470919</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>64,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6388,32 +6388,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4476212</t>
+          <t>4664389</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3946073</t>
+          <t>4589810</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4718416</t>
+          <t>4755344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,54%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -6431,32 +6431,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1036880</t>
+          <t>841415</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>833796</t>
+          <t>786465</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1623220</t>
+          <t>897278</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6466,32 +6466,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>788978</t>
+          <t>855345</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>651072</t>
+          <t>804717</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>857734</t>
+          <t>903043</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6501,32 +6501,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1825858</t>
+          <t>1696760</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1602955</t>
+          <t>1614387</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>2546583</t>
+          <t>1769186</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -6544,17 +6544,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3450869</t>
+          <t>3519597</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3450869</t>
+          <t>3519597</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3450869</t>
+          <t>3519597</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6579,17 +6579,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6614,17 +6614,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7104663</t>
+          <t>7247904</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7104663</t>
+          <t>7247904</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7104663</t>
+          <t>7247904</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
